--- a/battery_price_impact.xlsx
+++ b/battery_price_impact.xlsx
@@ -8894,7 +8894,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 identification threshold; admitted by documented exception</t>
+          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 price-ordering threshold; admitted by documented exception</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 identification threshold; admitted by documented exception</t>
+          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 price-ordering threshold; admitted by documented exception</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 identification threshold; admitted by documented exception</t>
+          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 price-ordering threshold; admitted by documented exception</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 identification threshold; admitted by documented exception</t>
+          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 price-ordering threshold; admitted by documented exception</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 identification threshold; admitted by documented exception</t>
+          <t>rho_top_q 0.5636 is 0.0364 short of the 0.60 price-ordering threshold; admitted by documented exception</t>
         </is>
       </c>
     </row>
